--- a/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007</t>
+          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49237</t>
+          <t>49125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>28336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>53159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>59729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92320</t>
+          <t>93959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442922</t>
+          <t>443034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466205</t>
+          <t>466450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414739</t>
+          <t>413391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438034</t>
+          <t>438214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866389</t>
+          <t>864750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>899443</t>
+          <t>898980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61051</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>37346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63355</t>
+          <t>65047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76300</t>
+          <t>76105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115214</t>
+          <t>117672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>671003</t>
+          <t>670638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>699752</t>
+          <t>698752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>560124</t>
+          <t>558432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587325</t>
+          <t>586133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1240319</t>
+          <t>1237861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1279233</t>
+          <t>1279428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39299</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>41641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74731</t>
+          <t>73269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66155</t>
+          <t>65143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102519</t>
+          <t>100903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597235</t>
+          <t>597137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619976</t>
+          <t>619427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615013</t>
+          <t>616475</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646014</t>
+          <t>648103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1223759</t>
+          <t>1225375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1260123</t>
+          <t>1261135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32578</t>
+          <t>33660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60281</t>
+          <t>62084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487194</t>
+          <t>487162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504639</t>
+          <t>504860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>473612</t>
+          <t>474724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494784</t>
+          <t>494585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>968420</t>
+          <t>966617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>996123</t>
+          <t>995041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>24106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>26731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>44756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361503</t>
+          <t>362604</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377567</t>
+          <t>377513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>378019</t>
+          <t>377255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394299</t>
+          <t>393659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>746658</t>
+          <t>745940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>768155</t>
+          <t>768906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275239</t>
+          <t>274403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286892</t>
+          <t>286987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>328597</t>
+          <t>327784</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338235</t>
+          <t>338161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>608113</t>
+          <t>607713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>622890</t>
+          <t>623293</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199736</t>
+          <t>199976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208220</t>
+          <t>208247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320077</t>
+          <t>319172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331576</t>
+          <t>330534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524408</t>
+          <t>523839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537740</t>
+          <t>538088</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183004</t>
+          <t>187136</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232663</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322844</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>400050</t>
+          <t>399602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3083118</t>
+          <t>3078986</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3134102</t>
+          <t>3132178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3137619</t>
+          <t>3138991</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3196098</t>
+          <t>3196962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6236354</t>
+          <t>6236802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6313560</t>
+          <t>6313260</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012</t>
+          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53690</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48302</t>
+          <t>48521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79505</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417885</t>
+          <t>418745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438329</t>
+          <t>438081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376540</t>
+          <t>376779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401182</t>
+          <t>401406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803558</t>
+          <t>803059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834761</t>
+          <t>834542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45644</t>
+          <t>45903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73797</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74435</t>
+          <t>74794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112034</t>
+          <t>111815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>642006</t>
+          <t>642051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>665016</t>
+          <t>665945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>535520</t>
+          <t>533648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563673</t>
+          <t>563414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1184370</t>
+          <t>1184589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1221969</t>
+          <t>1221610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66798</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93303</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105711</t>
+          <t>105726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149036</t>
+          <t>149029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615065</t>
+          <t>614075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641808</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616549</t>
+          <t>617322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651775</t>
+          <t>650943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242679</t>
+          <t>1242686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286004</t>
+          <t>1285989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>39408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37316</t>
+          <t>37734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67634</t>
+          <t>67648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>568854</t>
+          <t>567981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>589959</t>
+          <t>589393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>572523</t>
+          <t>573676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>594201</t>
+          <t>595224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1149791</t>
+          <t>1149777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1180109</t>
+          <t>1179691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21858</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37032</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407264</t>
+          <t>407266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422232</t>
+          <t>422883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>423706</t>
+          <t>423718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>437899</t>
+          <t>438285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>837961</t>
+          <t>837258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>857491</t>
+          <t>857511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291153</t>
+          <t>290275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343652</t>
+          <t>344171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352041</t>
+          <t>352037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>638974</t>
+          <t>639331</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654492</t>
+          <t>654463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235229</t>
+          <t>234944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245607</t>
+          <t>244647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373340</t>
+          <t>372908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383545</t>
+          <t>383536</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>613135</t>
+          <t>613552</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>626990</t>
+          <t>626888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140369</t>
+          <t>137796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193221</t>
+          <t>188694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>192329</t>
+          <t>190703</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>250007</t>
+          <t>249600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>342485</t>
+          <t>348380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421320</t>
+          <t>421226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3220899</t>
+          <t>3225426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3273751</t>
+          <t>3276324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3293674</t>
+          <t>3294081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3351352</t>
+          <t>3352978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6536481</t>
+          <t>6536575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6615316</t>
+          <t>6609421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016</t>
+          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>45152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37981</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75122</t>
+          <t>78070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373364</t>
+          <t>373199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395507</t>
+          <t>396845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353824</t>
+          <t>353324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373679</t>
+          <t>373724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735034</t>
+          <t>732086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765902</t>
+          <t>764496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51904</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52126</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85472</t>
+          <t>83590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>534600</t>
+          <t>534425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>559535</t>
+          <t>559998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516734</t>
+          <t>516124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537335</t>
+          <t>536482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1058796</t>
+          <t>1060678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1092142</t>
+          <t>1091768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43841</t>
+          <t>42790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34581</t>
+          <t>34507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60243</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61655</t>
+          <t>61255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94905</t>
+          <t>96309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623601</t>
+          <t>624652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646487</t>
+          <t>647693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>601143</t>
+          <t>601241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626805</t>
+          <t>626879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1233923</t>
+          <t>1232519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1267173</t>
+          <t>1267573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>38135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>36642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66886</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>605352</t>
+          <t>602395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>627041</t>
+          <t>626869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608852</t>
+          <t>607743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628772</t>
+          <t>627854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1220940</t>
+          <t>1220250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1250825</t>
+          <t>1251184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38420</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454000</t>
+          <t>451912</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469177</t>
+          <t>468565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>470113</t>
+          <t>469776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486458</t>
+          <t>487417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>931024</t>
+          <t>929293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>951590</t>
+          <t>953346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>319952</t>
+          <t>319191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330384</t>
+          <t>329490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359529</t>
+          <t>358968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372959</t>
+          <t>372470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684049</t>
+          <t>683995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>700168</t>
+          <t>700228</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243856</t>
+          <t>244486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253050</t>
+          <t>253659</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383307</t>
+          <t>380548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395603</t>
+          <t>394860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>631536</t>
+          <t>631967</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>647138</t>
+          <t>647218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>122364</t>
+          <t>121449</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171312</t>
+          <t>167990</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>136608</t>
+          <t>138065</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>188378</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>270888</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>340004</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3203692</t>
+          <t>3207014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3252640</t>
+          <t>3253555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3337833</t>
+          <t>3336364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3389603</t>
+          <t>3388146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6561212</t>
+          <t>6561321</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6630518</t>
+          <t>6630328</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023</t>
+          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>39595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21003</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62418</t>
+          <t>62336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358533</t>
+          <t>354798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388538</t>
+          <t>388109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273128</t>
+          <t>273605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300513</t>
+          <t>301089</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643482</t>
+          <t>643564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684897</t>
+          <t>686677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23004</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408850</t>
+          <t>406323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421843</t>
+          <t>422018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489503</t>
+          <t>489698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502421</t>
+          <t>502817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905805</t>
+          <t>905903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921965</t>
+          <t>922156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>33924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>40456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,47 +10406,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>51667</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>38137</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>66770</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>51667</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>38282</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>66878</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499939</t>
+          <t>499241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519325</t>
+          <t>519377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551162</t>
+          <t>550212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570636</t>
+          <t>569789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,47 +10519,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1072165</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1057062</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1085695</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>96,61%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1072165</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1056954</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1085550</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31540</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>26444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853407</t>
+          <t>854002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877760</t>
+          <t>877941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679002</t>
+          <t>678644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692724</t>
+          <t>693065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1540670</t>
+          <t>1538660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1568168</t>
+          <t>1568990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>21427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535860</t>
+          <t>534245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550068</t>
+          <t>549672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527548</t>
+          <t>527676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535377</t>
+          <t>535279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1067269</t>
+          <t>1066839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1083789</t>
+          <t>1082894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352572</t>
+          <t>352855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361702</t>
+          <t>361777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>595880</t>
+          <t>595501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602509</t>
+          <t>602516</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>950978</t>
+          <t>951959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>963914</t>
+          <t>963896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271114</t>
+          <t>271494</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277318</t>
+          <t>277311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>415275</t>
+          <t>415066</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>420202</t>
+          <t>420201</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>689328</t>
+          <t>689771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>697033</t>
+          <t>696864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>56103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105425</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114945</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137769</t>
+          <t>136957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>201908</t>
+          <t>201799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3327070</t>
+          <t>3332304</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3375859</t>
+          <t>3376392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3562794</t>
+          <t>3563730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3607149</t>
+          <t>3608322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6908326</t>
+          <t>6908435</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6972465</t>
+          <t>6973277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53159</t>
+          <t>52130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59729</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93959</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443034</t>
+          <t>443482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466450</t>
+          <t>467242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413391</t>
+          <t>414420</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438214</t>
+          <t>437710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>864750</t>
+          <t>865625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>898980</t>
+          <t>898582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>33107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61416</t>
+          <t>62003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>35972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65047</t>
+          <t>65142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76105</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117672</t>
+          <t>116443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670638</t>
+          <t>670051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>698752</t>
+          <t>698947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558432</t>
+          <t>558337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>586133</t>
+          <t>587507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1237861</t>
+          <t>1239090</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1279428</t>
+          <t>1281315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41641</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73269</t>
+          <t>73192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65143</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100903</t>
+          <t>103159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597137</t>
+          <t>597401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619427</t>
+          <t>620181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616475</t>
+          <t>616552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648103</t>
+          <t>646130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225375</t>
+          <t>1223119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261135</t>
+          <t>1259882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62084</t>
+          <t>59841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487162</t>
+          <t>484666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504860</t>
+          <t>504133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>474724</t>
+          <t>474898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494585</t>
+          <t>495602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>966617</t>
+          <t>968860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>995041</t>
+          <t>994527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44756</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>362604</t>
+          <t>362157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377513</t>
+          <t>377128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>377255</t>
+          <t>377252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393659</t>
+          <t>394098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>745940</t>
+          <t>747164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>768906</t>
+          <t>769104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274403</t>
+          <t>274461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286987</t>
+          <t>286771</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>327784</t>
+          <t>327736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338161</t>
+          <t>338147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607713</t>
+          <t>606911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623293</t>
+          <t>623116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199976</t>
+          <t>200556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208247</t>
+          <t>208213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319172</t>
+          <t>319299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330534</t>
+          <t>331567</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523839</t>
+          <t>524120</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>538088</t>
+          <t>538097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133944</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>187136</t>
+          <t>185742</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>173320</t>
+          <t>174603</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231291</t>
+          <t>230064</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>319328</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>399602</t>
+          <t>394110</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3078986</t>
+          <t>3080380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3132178</t>
+          <t>3133008</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3138991</t>
+          <t>3140218</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3196962</t>
+          <t>3195679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6236802</t>
+          <t>6242294</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6313260</t>
+          <t>6317076</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>34980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>29209</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80004</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418745</t>
+          <t>417853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438081</t>
+          <t>438245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376779</t>
+          <t>376963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401406</t>
+          <t>401021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803059</t>
+          <t>804163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834542</t>
+          <t>834403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>46592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45903</t>
+          <t>45533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75669</t>
+          <t>75152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74794</t>
+          <t>75043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111815</t>
+          <t>111662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>642051</t>
+          <t>640495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>665945</t>
+          <t>664417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>533648</t>
+          <t>534165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563414</t>
+          <t>563784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1184589</t>
+          <t>1184742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1221610</t>
+          <t>1221361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67788</t>
+          <t>68943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58909</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92530</t>
+          <t>91766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>107179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149029</t>
+          <t>148348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614075</t>
+          <t>612920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642215</t>
+          <t>641978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617322</t>
+          <t>618086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650943</t>
+          <t>652511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242686</t>
+          <t>1243367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1285989</t>
+          <t>1284536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39408</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36360</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37734</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67648</t>
+          <t>67777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>567981</t>
+          <t>568070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>589393</t>
+          <t>588947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573676</t>
+          <t>573683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>595224</t>
+          <t>594227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1149777</t>
+          <t>1149648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1179691</t>
+          <t>1179730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37735</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407266</t>
+          <t>407914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422883</t>
+          <t>422833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>423718</t>
+          <t>423099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438285</t>
+          <t>438378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>837258</t>
+          <t>837848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>857511</t>
+          <t>858364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290275</t>
+          <t>289523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303440</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344171</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352037</t>
+          <t>352039</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>639331</t>
+          <t>639423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654463</t>
+          <t>654230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234944</t>
+          <t>234137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244647</t>
+          <t>244643</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372908</t>
+          <t>371386</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383536</t>
+          <t>383516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>613552</t>
+          <t>612339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>626888</t>
+          <t>627030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137796</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188694</t>
+          <t>188220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190703</t>
+          <t>193119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249600</t>
+          <t>250564</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>348380</t>
+          <t>344656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421226</t>
+          <t>421901</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3225426</t>
+          <t>3225900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3276324</t>
+          <t>3274159</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3294081</t>
+          <t>3293117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3352978</t>
+          <t>3350562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6536575</t>
+          <t>6535900</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6609421</t>
+          <t>6613145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45660</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78070</t>
+          <t>76729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373199</t>
+          <t>372619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396845</t>
+          <t>396261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353324</t>
+          <t>352951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373724</t>
+          <t>373824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732086</t>
+          <t>733427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764496</t>
+          <t>764936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52079</t>
+          <t>49040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>21193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41640</t>
+          <t>42112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>85307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>534425</t>
+          <t>537464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>559998</t>
+          <t>560550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516124</t>
+          <t>515652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536482</t>
+          <t>536571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1060678</t>
+          <t>1058961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1091768</t>
+          <t>1091411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42790</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34507</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60145</t>
+          <t>59744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96309</t>
+          <t>94277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624652</t>
+          <t>625095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647693</t>
+          <t>646593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>601241</t>
+          <t>601642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626879</t>
+          <t>627306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1232519</t>
+          <t>1234551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1267573</t>
+          <t>1267933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>37976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36642</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602395</t>
+          <t>603972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>626869</t>
+          <t>626708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607743</t>
+          <t>608997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627854</t>
+          <t>628646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1220250</t>
+          <t>1219695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1251184</t>
+          <t>1249634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451912</t>
+          <t>454058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468565</t>
+          <t>468542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469776</t>
+          <t>469982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487417</t>
+          <t>487391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>929293</t>
+          <t>929640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>953346</t>
+          <t>951674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>25520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>319191</t>
+          <t>319453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329490</t>
+          <t>330393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>358968</t>
+          <t>359541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372470</t>
+          <t>372595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>683995</t>
+          <t>683695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>700228</t>
+          <t>700694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244486</t>
+          <t>244094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253659</t>
+          <t>253663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380548</t>
+          <t>382167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394860</t>
+          <t>395605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>631967</t>
+          <t>631461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>647218</t>
+          <t>647133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>121449</t>
+          <t>121365</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167990</t>
+          <t>171510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>138065</t>
+          <t>135844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189847</t>
+          <t>185701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>270054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>339993</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3207014</t>
+          <t>3203494</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3253555</t>
+          <t>3253639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3336364</t>
+          <t>3340510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3388146</t>
+          <t>3390367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6561321</t>
+          <t>6561223</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6630328</t>
+          <t>6631162</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>29736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>39226</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>24785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62336</t>
+          <t>63176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>379785</t>
+          <t>387900</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354798</t>
+          <t>370459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388109</t>
+          <t>395431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>290404</t>
+          <t>335581</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273605</t>
+          <t>318011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301089</t>
+          <t>347477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>670189</t>
+          <t>723482</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643564</t>
+          <t>699532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>686677</t>
+          <t>737923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>392700</t>
+          <t>400195</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>392700</t>
+          <t>400195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>392700</t>
+          <t>400195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>705900</t>
+          <t>762708</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>705900</t>
+          <t>762708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>705900</t>
+          <t>762708</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>418368</t>
+          <t>469255</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406323</t>
+          <t>458603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422018</t>
+          <t>473198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>497792</t>
+          <t>482157</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489698</t>
+          <t>472636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502817</t>
+          <t>488243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>916160</t>
+          <t>951412</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905903</t>
+          <t>940205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922156</t>
+          <t>959552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422348</t>
+          <t>475587</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422348</t>
+          <t>475587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422348</t>
+          <t>475587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>506461</t>
+          <t>495844</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>506461</t>
+          <t>495844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>506461</t>
+          <t>495844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>928809</t>
+          <t>971431</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>928809</t>
+          <t>971431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>928809</t>
+          <t>971431</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>31343</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>44363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29557</t>
+          <t>43447</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20879</t>
+          <t>33342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40456</t>
+          <t>55351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>74790</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66770</t>
+          <t>90771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>511055</t>
+          <t>585380</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499241</t>
+          <t>572360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519377</t>
+          <t>595783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>561111</t>
+          <t>577601</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>550212</t>
+          <t>565697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>569789</t>
+          <t>587706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1072165</t>
+          <t>1162981</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1057062</t>
+          <t>1147000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1085695</t>
+          <t>1178394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533165</t>
+          <t>616723</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533165</t>
+          <t>616723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533165</t>
+          <t>616723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>590668</t>
+          <t>621048</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>590668</t>
+          <t>621048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>590668</t>
+          <t>621048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1123832</t>
+          <t>1237771</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1123832</t>
+          <t>1237771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1123832</t>
+          <t>1237771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30945</t>
+          <t>34054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36505</t>
+          <t>45291</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51375</t>
+          <t>59111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866994</t>
+          <t>675099</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854002</t>
+          <t>663661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877941</t>
+          <t>683598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>686536</t>
+          <t>704893</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678644</t>
+          <t>695398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693065</t>
+          <t>710841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1553530</t>
+          <t>1379992</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1538660</t>
+          <t>1366172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1568990</t>
+          <t>1390668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>884947</t>
+          <t>697715</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>884947</t>
+          <t>697715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>884947</t>
+          <t>697715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>705088</t>
+          <t>727568</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>705088</t>
+          <t>727568</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>705088</t>
+          <t>727568</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1590035</t>
+          <t>1425283</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1590035</t>
+          <t>1425283</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1590035</t>
+          <t>1425283</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>544707</t>
+          <t>590675</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534245</t>
+          <t>581465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>549672</t>
+          <t>596231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>532068</t>
+          <t>592745</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527676</t>
+          <t>587844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535279</t>
+          <t>596462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1076774</t>
+          <t>1183420</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1066839</t>
+          <t>1174238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1082894</t>
+          <t>1190794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>555672</t>
+          <t>603482</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>555672</t>
+          <t>603482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>555672</t>
+          <t>603482</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>538870</t>
+          <t>600574</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>538870</t>
+          <t>600574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>538870</t>
+          <t>600574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1094541</t>
+          <t>1204056</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1094541</t>
+          <t>1204056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1094541</t>
+          <t>1204056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358308</t>
+          <t>396757</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352855</t>
+          <t>390378</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361777</t>
+          <t>400426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>599995</t>
+          <t>429578</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>595501</t>
+          <t>424827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602516</t>
+          <t>432161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>958303</t>
+          <t>826335</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>951959</t>
+          <t>819585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>963896</t>
+          <t>831529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365514</t>
+          <t>404444</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365514</t>
+          <t>404444</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365514</t>
+          <t>404444</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>603092</t>
+          <t>433509</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>603092</t>
+          <t>433509</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>603092</t>
+          <t>433509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>968606</t>
+          <t>837953</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>968606</t>
+          <t>837953</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>968606</t>
+          <t>837953</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>275432</t>
+          <t>302140</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271494</t>
+          <t>297045</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277311</t>
+          <t>304619</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>418849</t>
+          <t>456578</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>415066</t>
+          <t>452149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>420201</t>
+          <t>458047</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>694280</t>
+          <t>758718</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>689771</t>
+          <t>753563</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>696864</t>
+          <t>761975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>278150</t>
+          <t>305425</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>278150</t>
+          <t>305425</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>278150</t>
+          <t>305425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>420361</t>
+          <t>458689</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>420361</t>
+          <t>458689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>420361</t>
+          <t>458689</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>764114</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>764114</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>764114</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56103</t>
+          <t>76391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>118263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>101730</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>144358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>216975</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136957</t>
+          <t>189584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>201799</t>
+          <t>248382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3354647</t>
+          <t>3407205</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3332304</t>
+          <t>3385307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3376392</t>
+          <t>3427179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3586753</t>
+          <t>3579134</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3563730</t>
+          <t>3555387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3608322</t>
+          <t>3598015</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6941400</t>
+          <t>6986341</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6908435</t>
+          <t>6954934</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6973277</t>
+          <t>7013732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
